--- a/artfynd/A 29302-2022 artfynd.xlsx
+++ b/artfynd/A 29302-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 29302-2022 artfynd.xlsx
+++ b/artfynd/A 29302-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>527190</v>
       </c>
       <c r="B2" t="n">
-        <v>89742</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533921.4859484747</v>
+        <v>533921</v>
       </c>
       <c r="R2" t="n">
-        <v>7043658.423318766</v>
+        <v>7043658</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2012-10-10</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2012-10-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1873230</v>
+        <v>488273</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95769</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>2412</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Philonotis fontana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533895.3101782884</v>
+        <v>533954</v>
       </c>
       <c r="R3" t="n">
-        <v>7043766.158917692</v>
+        <v>7043752</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,19 +844,9 @@
           <t>2012-10-10</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2012-10-10</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,6 +870,208 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1873230</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Tannsjöberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>533895</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7043766</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2012-10-10</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2012-10-10</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>SCA Naturvärdesinventeringar</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Åsa Stenman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1875300</v>
+      </c>
+      <c r="B5" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Tannsjöberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>533956</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7043736</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2012-10-10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2012-10-10</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>SCA Naturvärdesinventeringar</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Åsa Stenman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>

--- a/artfynd/A 29302-2022 artfynd.xlsx
+++ b/artfynd/A 29302-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/527190</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/488273</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1873230</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,8 +1096,19 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1875300</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>